--- a/coded_corpus_v2.xlsx
+++ b/coded_corpus_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/upasanaroy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{616C5743-FFA6-3C48-8187-46DB18B0893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{57630ADB-E3FF-974B-9FF6-52AA84957B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16160" xr2:uid="{E70473BB-01CF-F94F-AEA1-1DA8DE8974A4}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="202">
   <si>
     <t>system_id</t>
   </si>
@@ -106,24 +106,15 @@
     <t>Chemistry</t>
   </si>
   <si>
-    <t>design;execution;interpretation</t>
-  </si>
-  <si>
     <t>G3</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>VERIFY</t>
-  </si>
-  <si>
     <t>delegate</t>
   </si>
   <si>
-    <t>goal-setter;gatekeeper</t>
-  </si>
-  <si>
     <t>robotic-labos</t>
   </si>
   <si>
@@ -142,12 +133,6 @@
     <t>substance-screening</t>
   </si>
   <si>
-    <t>none-reported</t>
-  </si>
-  <si>
-    <t>Bounded reaction family; scaffolding effort not quantified</t>
-  </si>
-  <si>
     <t>S02</t>
   </si>
   <si>
@@ -166,12 +151,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>operator;verifier</t>
-  </si>
-  <si>
-    <t>Worked boundary case for Sec III-C</t>
-  </si>
-  <si>
     <t>S03</t>
   </si>
   <si>
@@ -196,15 +175,9 @@
     <t>measured-rate</t>
   </si>
   <si>
-    <t>688 experiments / 8 days</t>
-  </si>
-  <si>
     <t>not-reported</t>
   </si>
   <si>
-    <t>Narrow epistemic role</t>
-  </si>
-  <si>
     <t>S04</t>
   </si>
   <si>
@@ -227,9 +200,6 @@
   </si>
   <si>
     <t>formal-logs</t>
-  </si>
-  <si>
-    <t>Strongest provenance in corpus</t>
   </si>
   <si>
     <t>S05</t>
@@ -492,21 +462,6 @@
     <t>papers reported to exceed a top-ML-conference acceptance threshold as judged by the authors' own automated reviewer, which they report as near-human on paper scoring; under $15 per paper; never submitted to human peer review</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">three ML subfields (diffusion modelling; transformer language modelling; learning dynamics); papers generated per subfield </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VERIFY</t>
-    </r>
-  </si>
-  <si>
     <t>v1 required a human-authored code template per topic area and ran a strictly linear experimentation loop; v2 removed both explicitly to raise autonomy, so the template requirement should be recorded against the laundered-human-effort failure mode of Section VII. Authors report the system modifying its own execution script to extend its timeout.</t>
   </si>
   <si>
@@ -600,6 +555,81 @@
   </si>
   <si>
     <t>https://www.science.org/doi/10.1126/science.1165620</t>
+  </si>
+  <si>
+    <t>Adam abduces hypotheses about genes encoding orphan enzymes from a yeast metabolism model, selects and runs differential-growth experiments on its own automation, and interprets the biomass measurements; the paper reports autonomous cycles without human intervention and up to a thousand strain and defined-growth-medium experiments per day</t>
+  </si>
+  <si>
+    <t>supervisor;verifier</t>
+  </si>
+  <si>
+    <t>12 previously unevidenced hypotheses confirmed at P&lt;0.05; 6 of the targeted enzymes proved not to be orphans owing to an incomplete bioinformatic database, serving as a positive control</t>
+  </si>
+  <si>
+    <t>~1000 strain/medium experiments per day; individual experiments up to 5 days; 6.6 million biomass measurements; &gt;10000 research units</t>
+  </si>
+  <si>
+    <t>Provenance is the strongest in the corpus: all aspects of the investigation are formalised in logic using LABORS, a customised version of the EXPO ontology expressed in OWL-DL, producing a nested tree of over 10000 research units ten levels deep linking every biomass measurement to its logical description. The authors confirmed Adam's conclusions through manual experiments, which is author-run verification rather than an outside check. Coded from the abstract and open full text; Science.org blocks automated access.</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41586-020-2442-2</t>
+  </si>
+  <si>
+    <t>the robot operated autonomously over eight days performing 688 experiments in a ten-variable space, driven by a batched Bayesian search algorithm; Fig. 2 (hypothesis-led autonomous search strategy) and Fig. 3 (output from the autonomous robotic search) show GC hydrogen measurements returning to the optimizer, which selects the next batch</t>
+  </si>
+  <si>
+    <t>goal-setter;operator</t>
+  </si>
+  <si>
+    <t>photocatalyst mixtures six times more active than the initial formulations; beneficial components selected and negative ones deselected; of 30 bioderived scavengers trialled, only cysteine competed with triethanolamine</t>
+  </si>
+  <si>
+    <t>688 experiments over 8 days; 46 batches of 16; ten-variable space; ~60 min photolysis plus ~28 min load/unload per batch</t>
+  </si>
+  <si>
+    <t>Correcting an earlier code of not-reported for provenance: the full autonomous-search dataset is released as Supplementary Data (CSV) containing optimizer-suggested masses and volumes, measured masses and volumes, and GC hydrogen measurements; workflow, labware designs, robot code and Bayesian optimizer are on Bitbucket and GitHub. Coded released-traces rather than formal-logs because the record shows what was proposed and measured, not a re-derivable logical account of why. Humans set the five hypotheses and the ten-variable search space beforehand and restocked consumables, so the epistemic role is optimization within a human-framed space; the authors describe the strategy as automating the researcher rather than the instruments, and the laboratory was otherwise unmodified apart from location cubes.</t>
+  </si>
+  <si>
+    <t>can you fill up all the columns of the csv file referring the possible values allowed from the readme file you gave me</t>
+  </si>
+  <si>
+    <t>operator;approver;verifier</t>
+  </si>
+  <si>
+    <t>four syntheses yielded the anticipated compounds; a proposed novel chromophore was synthesized with measured absorption maximum 336 nm against a 369 nm target; expert chemists (n=4) preferred ChemCrow over tool-less GPT-4 on chemical accuracy and task completion across 14 use cases</t>
+  </si>
+  <si>
+    <t>4 robotic syntheses (DEET + 3 organocatalysts); 1 chromophore discovery loop; 14 evaluation use cases; 56 human and 14 LLM assessments</t>
+  </si>
+  <si>
+    <t>Two corrections. Provenance: all experiment runs are released at github.com/ur-whitelab/chemcrow-runs (Zenodo 10.5281/zenodo.10884645) and an open-source platform with 12 of the 18 tools at chemcrow-public, so released-traces rather than tool-call-logs. Safety: three dedicated tools, ControlledChemicalCheck against OPCW Schedules 1-3 and the Australia Group export list with a 0.35 Tanimoto similarity warning threshold, ExplosiveCheck against GHS ratings, and SafetySummary; the first two are invoked automatically whenever a synthesis is requested and execution halts if the molecule is listed. The ReactionExecute tool also requests user permission before launching, which is an approval gate. Clause (iii) is arguably Y within a single synthesis: ChemCrow queries validation data from RoboRXN and iteratively adapts the procedure until valid. We code it as feedback on procedure validity rather than on experimental outcome, so the G2 assignment stands either way since clause (i) fails.</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41586-023-06792-0</t>
+  </si>
+  <si>
+    <t>Section Integrated chemical experiment design: 'Although our setup is not yet fully automated (plates were moved manually), no human decision-making was involved.' Clause (i) holds since Coscientist selected reagents and wrote the protocol unaided, but clause (ii) fails on manual plate transfer and clause (iii) fails because GC-MS analysis was performed and interpreted by the authors. Authors describe the system as '(semi-)autonomous' in both the abstract and Discussion</t>
+  </si>
+  <si>
+    <t>Section Autonomous chemical synthesis: from a natural-language prompt ChemCrow queried tools, planned syntheses and executed them on IBM's cloud-connected RoboRXN platform, synthesizing DEET and three thiourea organocatalysts; the ReactionExecute tool requests user permission before launching each synthesis, so clause (i) fails and the system is G2</t>
+  </si>
+  <si>
+    <t>goal-setter;operator;verifier</t>
+  </si>
+  <si>
+    <t>Suzuki and Sonogashira products confirmed by GC-MS against pure standards; Web Searcher scored maximum on 4 of 7 synthesis-planning targets against GPT-4, GPT-3.5, Claude 1.3 and Falcon-40B baselines; GPT-4-based optimization exceeded Bayesian optimization on normalized maximum advantage over 20 iterations</t>
+  </si>
+  <si>
+    <t>6 demonstration tasks; 2 physical cross-coupling reactions; 7-compound synthesis-planning benchmark; 20-iteration optimization game on two literature datasets</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>Recoded from G3 to G2. Clause (ii) fails on manual plate transfer, which the paper states directly. Clause (iii) fails for the cross-coupling campaign, though it holds in the isolated UV-Vis colours task where measurements returned as a NumPy array and Coscientist wrote analysis code; that task required a guiding prompt and was a single demonstration rather than a sustained loop. Provenance is not-reported by deliberate choice: 'because of safety concerns, data, code and prompts will be only fully released after the development of US regulations', with only a simpler implementation at github.com/gomesgroup/coscientist. Safety is an isolated Docker container for code execution plus a dual-use study in the Supplementary Information; no substance screening comparable to ChemCrow. Two co-authors have Emerald Cloud Lab affiliations and two are aithera.ai co-founders.</t>
+  </si>
+  <si>
+    <t>three ML subfields (diffusion modelling; transformer language modelling; learning dynamics)</t>
   </si>
 </sst>
 </file>
@@ -939,12 +969,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1059,6 +1089,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1107,22 +1152,20 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="42" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1502,1254 +1545,1264 @@
   <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.6640625" customWidth="1"/>
-    <col min="15" max="15" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="78.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="87" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="1" customFormat="1" ht="187" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2023</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="1" customFormat="1" ht="170" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" s="1" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2020</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2009</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="1" customFormat="1" ht="187" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2015</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" s="1" customFormat="1" ht="187" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" s="1" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2025</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="1" customFormat="1" ht="170" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2023</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" s="1" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
+      <c r="O10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2">
-        <v>2023</v>
-      </c>
-      <c r="F2" t="s">
+    <row r="11" spans="1:25" s="1" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2025</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="1" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2018</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" s="1" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2024</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>39</v>
-      </c>
-      <c r="W2" t="s">
-        <v>59</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Q14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y14" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2025</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="N15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2025</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="I16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3">
-        <v>2024</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="J16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W3" t="s">
-        <v>59</v>
-      </c>
-      <c r="X3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4">
-        <v>2020</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S4" t="s">
-        <v>58</v>
-      </c>
-      <c r="T4" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" t="s">
-        <v>59</v>
-      </c>
-      <c r="V4" t="s">
-        <v>59</v>
-      </c>
-      <c r="W4" t="s">
-        <v>59</v>
-      </c>
-      <c r="X4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2009</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" s="2" t="s">
+      <c r="R16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" s="5" customFormat="1" ht="204" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="5">
-        <v>2015</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" s="5" customFormat="1" ht="221" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E7" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y7" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" s="5" customFormat="1" ht="136" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y8" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" s="5" customFormat="1" ht="187" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" s="5">
-        <v>2023</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y9" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" s="5" customFormat="1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2024</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" s="5" customFormat="1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" s="5" customFormat="1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2018</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y12" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" s="5" customFormat="1" ht="170" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2024</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="T13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U13" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="V13" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="W13" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="X13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y13" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" s="5" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" s="5">
-        <v>2024</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="V14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y14" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" s="5" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="U16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y16" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="T15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y15" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" s="5" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" s="5">
-        <v>2025</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="T16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="W16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="X16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y16" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2766,6 +2819,8 @@
     <hyperlink ref="D7" r:id="rId10" xr:uid="{CBECDEF2-05CA-A643-AF91-977DC538B83B}"/>
     <hyperlink ref="D6" r:id="rId11" xr:uid="{51F4BAB3-569D-CE43-96D7-CAC37ED65FFE}"/>
     <hyperlink ref="D5" r:id="rId12" xr:uid="{E05ED4BC-70C8-DF49-9D09-CC8D2EE8B16D}"/>
+    <hyperlink ref="D4" r:id="rId13" xr:uid="{8236B931-C9AF-E842-B3E7-4AE66FC4D7DE}"/>
+    <hyperlink ref="D2" r:id="rId14" xr:uid="{F7ABF364-9591-4C47-967E-37F6740D7589}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
